--- a/output/tables/eTable2_Human_AI_Means_Rankings.xlsx
+++ b/output/tables/eTable2_Human_AI_Means_Rankings.xlsx
@@ -69,7 +69,7 @@
     <t>2.94 (0.02)</t>
   </si>
   <si>
-    <t>Sleep</t>
+    <t>Sleep disruption</t>
   </si>
   <si>
     <t>2.89 (0.04)</t>
